--- a/data/07_corporate_markets.xlsx
+++ b/data/07_corporate_markets.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R2607d3e2574f49ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R397878349f29436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R8b2a4c2293264448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R56c24626bddc40d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R2d53939a9df743f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R6aff471ad806478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R1ab0ed359fed4224"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R34a9e634ab514740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="Raf65d22d50624090"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R7d4a3d80f36e4eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="Ra46cd9b7a027484c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="Ra03a667be21e4309"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R4f9f0f52967b4aab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R7c85a4b376524a02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="Rf52ab9a737404635"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R91a2c66f92154cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R70bcea4a9b364626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="Rfa1d853bae9743aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R4e831eeff77b41c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R7ed9d63ed6434fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R3e26c299c9e64abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R5caaab2fc04543ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R7befb39aff2f4299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R066905654bde4053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R6489f83ef95b415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R691e0d8085bd4033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="Rc0583f4bd5b24d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="Rba380cd030884f6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R5e5447da27934623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="Rfdc253fc0c954248"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -76,7 +76,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -107,6 +107,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -724,6 +725,41 @@
         <x:v>Company delisted August 2026</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>RPT_V1251_ADP_2024</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>Annual report</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>FY2024</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>AD Ports Group Integrated Annual Report &amp; Accounts 2024</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>Includes official 2024 monthly share-price table</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1019,6 +1055,134 @@
       </x:c>
       <x:c r="J4" s="14" t="str">
         <x:v>Website description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>OPM_V1251_SEASPAN_01</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>Fleet vessels</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>vessels</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/sustainable-vessels/</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>Fully delivered basis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>OPM_V1251_SEASPAN_02</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>Fleet capacity</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>2400000</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>TEU</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/sustainable-vessels/</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>Approximate fully delivered capacity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>OPM_V1251_INOCEA_01</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>Major shipyard facilities</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>facilities</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>Shipbuilding</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>Canada / United States / Finland</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>Davie states Inocea operates five major shipyard facilities</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>OPM_V1251_DAVIE_01</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Program Icebreakers contracted</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>vessels</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>Shipbuilding</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>Canadian Coast Guard Program Icebreakers</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5846,6 +6010,846 @@
         <x:v>Last close cited immediately before offer; monthly series backfill pending</x:v>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>PRICE_ADP_100</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>2024-01-31</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str"/>
+      <x:c r="E4" s="14" t="n">
+        <x:v>6.45</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="n">
+        <x:v>6.18</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="n">
+        <x:v>6.21</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str"/>
+      <x:c r="I4" s="14" t="str"/>
+      <x:c r="J4" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>PRICE_ADP_101</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>2024-02-29</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str"/>
+      <x:c r="E5" s="14" t="n">
+        <x:v>6.27</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="n">
+        <x:v>5.46</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="n">
+        <x:v>5.79</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str"/>
+      <x:c r="I5" s="14" t="str"/>
+      <x:c r="J5" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L5" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M5" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>PRICE_ADP_102</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>2024-03-31</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str"/>
+      <x:c r="E6" s="14" t="n">
+        <x:v>5.94</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="n">
+        <x:v>5.41</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="n">
+        <x:v>5.76</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str"/>
+      <x:c r="I6" s="14" t="str"/>
+      <x:c r="J6" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>PRICE_ADP_103</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>2024-04-30</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str"/>
+      <x:c r="E7" s="14" t="n">
+        <x:v>5.99</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="n">
+        <x:v>5.22</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="n">
+        <x:v>5.81</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str"/>
+      <x:c r="I7" s="14" t="str"/>
+      <x:c r="J7" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>PRICE_ADP_104</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>2024-05-31</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str"/>
+      <x:c r="E8" s="14" t="n">
+        <x:v>5.87</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="n">
+        <x:v>5.08</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str"/>
+      <x:c r="I8" s="14" t="str"/>
+      <x:c r="J8" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L8" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>PRICE_ADP_105</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>2024-06-30</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str"/>
+      <x:c r="E9" s="14" t="n">
+        <x:v>5.27</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="n">
+        <x:v>4.96</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="n">
+        <x:v>5.1</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str"/>
+      <x:c r="I9" s="14" t="str"/>
+      <x:c r="J9" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L9" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>PRICE_ADP_106</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>2024-07-31</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str"/>
+      <x:c r="E10" s="14" t="n">
+        <x:v>5.29</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="n">
+        <x:v>4.95</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str"/>
+      <x:c r="I10" s="14" t="str"/>
+      <x:c r="J10" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L10" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>PRICE_ADP_107</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>2024-08-31</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str"/>
+      <x:c r="E11" s="14" t="n">
+        <x:v>5.19</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="n">
+        <x:v>4.73</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="n">
+        <x:v>4.79</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str"/>
+      <x:c r="I11" s="14" t="str"/>
+      <x:c r="J11" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>PRICE_ADP_108</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>2024-09-30</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str"/>
+      <x:c r="E12" s="14" t="n">
+        <x:v>5.22</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="n">
+        <x:v>4.79</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="n">
+        <x:v>5.11</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str"/>
+      <x:c r="I12" s="14" t="str"/>
+      <x:c r="J12" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>PRICE_ADP_109</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>2024-10-31</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str"/>
+      <x:c r="E13" s="14" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="n">
+        <x:v>5.35</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str"/>
+      <x:c r="I13" s="14" t="str"/>
+      <x:c r="J13" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L13" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>PRICE_ADP_110</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>2024-11-30</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str"/>
+      <x:c r="E14" s="14" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="n">
+        <x:v>4.91</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="n">
+        <x:v>4.96</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str"/>
+      <x:c r="I14" s="14" t="str"/>
+      <x:c r="J14" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L14" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>PRICE_ADP_111</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>2024-12-31</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str"/>
+      <x:c r="E15" s="14" t="n">
+        <x:v>5.1</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="n">
+        <x:v>4.73</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="n">
+        <x:v>5.09</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str"/>
+      <x:c r="I15" s="14" t="str"/>
+      <x:c r="J15" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="str">
+        <x:v>https://apigateway.adx.ae/adx/cdn/1.0/content/download/4314325</x:v>
+      </x:c>
+      <x:c r="L15" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="str">
+        <x:v>2024 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>PRICE_ADP_112</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>2025-01-31</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str"/>
+      <x:c r="E16" s="14" t="n">
+        <x:v>5.09</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str"/>
+      <x:c r="I16" s="14" t="str"/>
+      <x:c r="J16" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L16" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
+        <x:v>PRICE_ADP_113</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>2025-02-28</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str"/>
+      <x:c r="E17" s="14" t="n">
+        <x:v>5.01</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="n">
+        <x:v>4.56</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="n">
+        <x:v>4.57</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str"/>
+      <x:c r="I17" s="14" t="str"/>
+      <x:c r="J17" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L17" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14" t="str">
+        <x:v>PRICE_ADP_114</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>2025-03-31</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str"/>
+      <x:c r="E18" s="14" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str"/>
+      <x:c r="I18" s="14" t="str"/>
+      <x:c r="J18" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L18" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14" t="str">
+        <x:v>PRICE_ADP_115</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>2025-04-30</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str"/>
+      <x:c r="E19" s="14" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="n">
+        <x:v>3.97</x:v>
+      </x:c>
+      <x:c r="H19" s="14" t="str"/>
+      <x:c r="I19" s="14" t="str"/>
+      <x:c r="J19" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L19" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14" t="str">
+        <x:v>PRICE_ADP_116</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>2025-05-31</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str"/>
+      <x:c r="E20" s="14" t="n">
+        <x:v>4.04</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>3.88</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="n">
+        <x:v>3.99</x:v>
+      </x:c>
+      <x:c r="H20" s="14" t="str"/>
+      <x:c r="I20" s="14" t="str"/>
+      <x:c r="J20" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L20" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14" t="str">
+        <x:v>PRICE_ADP_117</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>2025-06-30</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str"/>
+      <x:c r="E21" s="14" t="n">
+        <x:v>4.15</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>3.49</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="n">
+        <x:v>4.07</x:v>
+      </x:c>
+      <x:c r="H21" s="14" t="str"/>
+      <x:c r="I21" s="14" t="str"/>
+      <x:c r="J21" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L21" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14" t="str">
+        <x:v>PRICE_ADP_118</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>2025-07-31</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str"/>
+      <x:c r="E22" s="14" t="n">
+        <x:v>4.45</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>3.96</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str"/>
+      <x:c r="I22" s="14" t="str"/>
+      <x:c r="J22" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L22" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14" t="str">
+        <x:v>PRICE_ADP_119</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>2025-08-31</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str"/>
+      <x:c r="E23" s="14" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>4.11</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str"/>
+      <x:c r="I23" s="14" t="str"/>
+      <x:c r="J23" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L23" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>PRICE_ADP_120</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>2025-09-30</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str"/>
+      <x:c r="E24" s="14" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>3.71</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str"/>
+      <x:c r="I24" s="14" t="str"/>
+      <x:c r="J24" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L24" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>PRICE_ADP_121</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>2025-10-31</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str"/>
+      <x:c r="E25" s="14" t="n">
+        <x:v>4.89</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>3.71</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="n">
+        <x:v>4.58</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str"/>
+      <x:c r="I25" s="14" t="str"/>
+      <x:c r="J25" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L25" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>PRICE_ADP_122</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>2025-11-30</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str"/>
+      <x:c r="E26" s="14" t="n">
+        <x:v>4.74</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="n">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="n">
+        <x:v>4.37</x:v>
+      </x:c>
+      <x:c r="H26" s="14" t="str"/>
+      <x:c r="I26" s="14" t="str"/>
+      <x:c r="J26" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L26" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>PRICE_ADP_123</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str"/>
+      <x:c r="E27" s="14" t="n">
+        <x:v>4.89</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="n">
+        <x:v>4.37</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="n">
+        <x:v>4.77</x:v>
+      </x:c>
+      <x:c r="H27" s="14" t="str"/>
+      <x:c r="I27" s="14" t="str"/>
+      <x:c r="J27" s="14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/-/media/sites/adports/investors/annual-report/adpg-annual-report-2025-en.pdf</x:v>
+      </x:c>
+      <x:c r="L27" s="14" t="str">
+        <x:v>Official annual-report monthly series</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="str">
+        <x:v>2025 monthly close/high/low</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/07_corporate_markets.xlsx
+++ b/data/07_corporate_markets.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R91a2c66f92154cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R70bcea4a9b364626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="Rfa1d853bae9743aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R4e831eeff77b41c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R7ed9d63ed6434fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R3e26c299c9e64abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R5caaab2fc04543ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R7befb39aff2f4299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R066905654bde4053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R6489f83ef95b415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R691e0d8085bd4033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="Rc0583f4bd5b24d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="Rba380cd030884f6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R5e5447da27934623"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="Rfdc253fc0c954248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rad5542a2c11c42dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R5e0383b66f734231"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R45bc784514d84a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R394658cbc3f642f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R544dbe24a63d4914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R4e1c7525f190464b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R252f4cc80b0f4c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R0a3c8100e8e44879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R0322832747124a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R6e0f88d9f3da48f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R465481c2fea84b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="R52eb8f781fc94457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R71d38b5b084b404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R34db89162f7e449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R51fbf364b5044755"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -908,6 +908,39 @@
         <x:v>Canonical MBS company ID to align if already present</x:v>
       </x:c>
     </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>FIN134_001</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>COMP_HUNTER_GROUP</x:v>
+      </x:c>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>Disputed charter-rate receivable</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>55000000</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>Tanker chartering</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>Claimed underpayment; amount increased by about USD 12m from the prior month. Counterparty identity not confirmed in the current article; court case pending.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/07_corporate_markets.xlsx
+++ b/data/07_corporate_markets.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rad5542a2c11c42dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R5e0383b66f734231"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R45bc784514d84a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R394658cbc3f642f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R544dbe24a63d4914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R4e1c7525f190464b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R252f4cc80b0f4c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R0a3c8100e8e44879"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R0322832747124a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R6e0f88d9f3da48f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R465481c2fea84b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="R52eb8f781fc94457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R71d38b5b084b404b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R34db89162f7e449e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R51fbf364b5044755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R5f11c20cd5704429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R666d4c9ca4be4793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R7c80b1df88964ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R04003efea8b249e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="Recab40bcd4e140dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R0f625c6f2b594df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R5fc42d8174c848ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R6f1b016039bb4103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="Rdc79be1b3a9941a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R2d70105ec5764489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R56a0871951b440ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="R58a4aa8a65514e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R1a9b50915dd3448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R06caf217de2141cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R5b0e70abadd54107"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -760,6 +760,41 @@
         <x:v>Includes official 2024 monthly share-price table</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Annual report / results</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>2026-03-12</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>DP World FY2025 results and annual report</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>https://www.dpworld.com/en/investors/annual-report-2025</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>Record 2025 financials and capital expenditure</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -941,6 +976,737 @@
         <x:v>Claimed underpayment; amount increased by about USD 12m from the prior month. Counterparty identity not confirmed in the current article; court case pending.</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>FIN_ADP_2025_REV</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>RPT_001</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>20770000000</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>FIN_ADP_2025_EBITDA</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>RPT_001</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>EBITDA</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>5110000000</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>FIN_ADP_2025_NP</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>RPT_001</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Net profit</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>2070000000</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>FIN_ADP_2025_CFO</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>RPT_001</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>5050000000</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/02/12/ad-ports-group-reports-record-2025-revenue</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>FIN_ADP_2025_CAPEX</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>RPT_001</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Organic CAPEX</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
+        <x:v>5500000000</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/02/12/ad-ports-group-reports-record-2025-revenue</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>FIN_ADP_2025_ASSETS</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>RPT_001</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Total assets</x:v>
+      </x:c>
+      <x:c r="F11" t="n">
+        <x:v>69420000000</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>FIN_ADP_Q2_26_REV</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="F12" t="n">
+        <x:v>7080000000</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>Q2 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>FIN_ADP_Q2_26_EBITDA</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>EBITDA</x:v>
+      </x:c>
+      <x:c r="F13" t="n">
+        <x:v>1740000000</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>Q2 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>FIN_ADP_Q2_26_NP</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Net profit</x:v>
+      </x:c>
+      <x:c r="F14" t="n">
+        <x:v>836000000</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>Q2 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>FIN_ADP_Q2_26_CFO</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="F15" t="n">
+        <x:v>2140000000</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>Q2 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>FIN_ADP_Q2_26_CAPEX</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Organic CAPEX</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>1450000000</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>Q2 2026; excludes GFS stake purchase</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>FIN_ADP_Q2_26_NETDEBT</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Net debt</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>22730000000</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>Q2 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>FIN_ADP_Q2_26_LEV</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Net debt / EBITDA</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>multiple</x:v>
+      </x:c>
+      <x:c r="H18"/>
+      <x:c r="I18" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>Q2 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>FIN_ADP_Q2_26_FCFF</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>RPT_002</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Free cash flow to firm</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>-1030000000</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>Includes AED1.1bn GFS stake acquisition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>FIN_DPW_2025_REV</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>24400000000</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>FIN_DPW_2025_EBITDA</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Adjusted EBITDA</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>6400000000</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>FIN_DPW_2025_PROFIT</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Profit for the year</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>1960000000</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>FIN_DPW_2025_CFO</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>6300000000</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>FIN_DPW_2025_CAPEX</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>3100000000</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>FY2025 actual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>FIN_DPW_2025_ROCE</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Return on capital employed</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H25"/>
+      <x:c r="I25" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>FIN_DPW_2026_CAPEX_BUDGET</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>RPT_006</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>2026-12-31</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>CAPEX budget</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>currency</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>Group</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>Approximate 2026 budget; not actual spend</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1216,6 +1982,134 @@
       </x:c>
       <x:c r="J8" s="14" t="str">
         <x:v>Canadian Coast Guard Program Icebreakers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>OPM_GULF_001</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>COMP_GULFTAINER</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Khorfakkan future port capacity</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>TEU</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Long-term masterplan exceeds 10m TEU</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>OPM_GULF_002</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>COMP_GULFTAINER</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Combined inland logistics capacity</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>2300000</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>TEU</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>Logistics / inland</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Al Dhaid and Sajaa combined</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>OPM_GULF_003</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>COMP_GULFTAINER</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>GT Lines fleet</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>chartered vessels</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>Regional / Asia</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Owned-vessel expansion underway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>OPM_DPW_2025_TEU</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Gross container throughput</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>93400000</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>TEU</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>FY2025</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3907,6 +4801,24 @@
       <x:c r="M1" s="11" t="str">
         <x:v>Source ID</x:v>
       </x:c>
+      <x:c r="N1" t="str">
+        <x:v>Investment Class</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>Spend Type</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>Region</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>Fiscal Year</x:v>
+      </x:c>
+      <x:c r="R1" t="str">
+        <x:v>Value Status</x:v>
+      </x:c>
+      <x:c r="S1" t="str">
+        <x:v>Investment Stage</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
@@ -3946,6 +4858,24 @@
       <x:c r="M2" s="14" t="str">
         <x:v>SRC_0031</x:v>
       </x:c>
+      <x:c r="N2" t="str">
+        <x:v>Infrastructure programme</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="Q2" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>Actual / ongoing</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
@@ -3987,6 +4917,24 @@
       <x:c r="M3" s="14" t="str">
         <x:v>SRC_0004</x:v>
       </x:c>
+      <x:c r="N3" t="str">
+        <x:v>Terminal development</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="Q3" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R3" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S3" t="str">
+        <x:v>Committed / development</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
@@ -4028,6 +4976,24 @@
       <x:c r="M4" s="14" t="str">
         <x:v>SRC_0028</x:v>
       </x:c>
+      <x:c r="N4" t="str">
+        <x:v>Acquisition / M&amp;A</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="Q4" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R4" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S4" t="str">
+        <x:v>Pending / committed</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -4069,6 +5035,24 @@
       <x:c r="M5" s="14" t="str">
         <x:v>SRC_0044</x:v>
       </x:c>
+      <x:c r="N5" t="str">
+        <x:v>Terminal expansion</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P5" t="str">
+        <x:v>Latin America</x:v>
+      </x:c>
+      <x:c r="Q5" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R5" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S5" t="str">
+        <x:v>Actual / commissioned</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
@@ -4110,6 +5094,24 @@
       <x:c r="M6" s="14" t="str">
         <x:v>SRC_0044</x:v>
       </x:c>
+      <x:c r="N6" t="str">
+        <x:v>Terminal expansion</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>Latin America</x:v>
+      </x:c>
+      <x:c r="Q6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R6" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S6" t="str">
+        <x:v>Committed / construction</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
@@ -4149,6 +5151,24 @@
       <x:c r="M7" s="14" t="str">
         <x:v>SRC_0018</x:v>
       </x:c>
+      <x:c r="N7" t="str">
+        <x:v>Terminal development</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>Latin America</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R7" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S7" t="str">
+        <x:v>Committed / development</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
@@ -4190,6 +5210,24 @@
       <x:c r="M8" s="14" t="str">
         <x:v>SRC_0034</x:v>
       </x:c>
+      <x:c r="N8" t="str">
+        <x:v>Infrastructure programme</x:v>
+      </x:c>
+      <x:c r="O8" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P8" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="R8" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S8" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -4229,6 +5267,24 @@
       <x:c r="M9" s="14" t="str">
         <x:v>SRC_0010</x:v>
       </x:c>
+      <x:c r="N9" t="str">
+        <x:v>Acquisition / M&amp;A</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>Latin America</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R9" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S9" t="str">
+        <x:v>Announced / pending</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
@@ -4267,6 +5323,24 @@
       </x:c>
       <x:c r="M10" s="14" t="str">
         <x:v>SRC_0010</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>Port infrastructure</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P10" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="Q10" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R10" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S10" t="str">
+        <x:v>Committed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4303,6 +5377,24 @@
       <x:c r="M11" s="14" t="str">
         <x:v>SRC_0041</x:v>
       </x:c>
+      <x:c r="N11" t="str">
+        <x:v>Logistics corridor development</x:v>
+      </x:c>
+      <x:c r="O11" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P11" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="Q11" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R11" t="str">
+        <x:v>Undisclosed</x:v>
+      </x:c>
+      <x:c r="S11" t="str">
+        <x:v>Committed / development</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -4342,6 +5434,24 @@
       <x:c r="M12" s="14" t="str">
         <x:v>SRC_0007</x:v>
       </x:c>
+      <x:c r="N12" t="str">
+        <x:v>Port infrastructure</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P12" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q12" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R12" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S12" t="str">
+        <x:v>Actual / ongoing</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
@@ -4381,6 +5491,24 @@
       <x:c r="M13" s="14" t="str">
         <x:v>SRC_0002</x:v>
       </x:c>
+      <x:c r="N13" t="str">
+        <x:v>Infrastructure programme</x:v>
+      </x:c>
+      <x:c r="O13" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P13" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="R13" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S13" t="str">
+        <x:v>Planned / multi-year</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
@@ -4422,6 +5550,24 @@
       <x:c r="M14" s="14" t="str">
         <x:v>SRC_0256</x:v>
       </x:c>
+      <x:c r="N14" t="str">
+        <x:v>Strategic equity investment</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>Equity investment</x:v>
+      </x:c>
+      <x:c r="P14" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="Q14" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R14" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S14" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
@@ -4463,6 +5609,24 @@
       <x:c r="M15" s="14" t="str">
         <x:v>SRC_0255</x:v>
       </x:c>
+      <x:c r="N15" t="str">
+        <x:v>Asset disposal</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>Divestment</x:v>
+      </x:c>
+      <x:c r="P15" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q15" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="R15" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S15" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
@@ -4502,6 +5666,24 @@
       <x:c r="M16" s="14" t="str">
         <x:v>SRC_0263</x:v>
       </x:c>
+      <x:c r="N16" t="str">
+        <x:v>Logistics real estate</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P16" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q16" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R16" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S16" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
@@ -4543,6 +5725,24 @@
       <x:c r="M17" s="14" t="str">
         <x:v>SRC_0267</x:v>
       </x:c>
+      <x:c r="N17" t="str">
+        <x:v>Logistics real estate</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>Equity investment</x:v>
+      </x:c>
+      <x:c r="P17" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="Q17" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R17" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S17" t="str">
+        <x:v>Formed</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
@@ -4582,6 +5782,24 @@
       <x:c r="M18" s="14" t="str">
         <x:v>SRC_0268</x:v>
       </x:c>
+      <x:c r="N18" t="str">
+        <x:v>Logistics real estate</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>Equity investment</x:v>
+      </x:c>
+      <x:c r="P18" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q18" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R18" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S18" t="str">
+        <x:v>Formed</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
@@ -4622,6 +5840,24 @@
       </x:c>
       <x:c r="M19" s="14" t="str">
         <x:v>SRC_0258</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>Acquisition / M&amp;A</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P19" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="Q19" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="R19" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S19" t="str">
+        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4658,6 +5894,24 @@
       <x:c r="M20" s="14" t="str">
         <x:v>SRC_0277</x:v>
       </x:c>
+      <x:c r="N20" t="str">
+        <x:v>Acquisition / M&amp;A</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P20" t="str">
+        <x:v>Central Asia / Caucasus</x:v>
+      </x:c>
+      <x:c r="Q20" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="R20" t="str">
+        <x:v>Undisclosed</x:v>
+      </x:c>
+      <x:c r="S20" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
@@ -4698,6 +5952,24 @@
       </x:c>
       <x:c r="M21" s="14" t="str">
         <x:v>SRC_0281</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>Economic zone development</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P21" t="str">
+        <x:v>Middle East / North Africa</x:v>
+      </x:c>
+      <x:c r="Q21" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="R21" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S21" t="str">
+        <x:v>Committed / development</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4734,6 +6006,24 @@
       <x:c r="M22" s="14" t="str">
         <x:v>SRC_0285</x:v>
       </x:c>
+      <x:c r="N22" t="str">
+        <x:v>Logistics real estate</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="Q22" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R22" t="str">
+        <x:v>Undisclosed</x:v>
+      </x:c>
+      <x:c r="S22" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
@@ -4773,6 +6063,24 @@
       <x:c r="M23" s="14" t="str">
         <x:v>SRC_0296</x:v>
       </x:c>
+      <x:c r="N23" t="str">
+        <x:v>Logistics hub development</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P23" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="Q23" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="R23" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S23" t="str">
+        <x:v>Committed / development</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
@@ -4814,6 +6122,24 @@
       <x:c r="M24" s="14" t="str">
         <x:v>SRC_0300</x:v>
       </x:c>
+      <x:c r="N24" t="str">
+        <x:v>Air cargo infrastructure</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P24" t="str">
+        <x:v>South Asia</x:v>
+      </x:c>
+      <x:c r="Q24" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R24" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S24" t="str">
+        <x:v>Committed / development</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
@@ -4854,6 +6180,478 @@
       </x:c>
       <x:c r="M25" s="14" t="str">
         <x:v>SRC_0306</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>Air cargo infrastructure</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="Q25" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="R25" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S25" t="str">
+        <x:v>Actual / operating</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>INV025</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>COMP_GULFTAINER</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Suksawat Terminal strategic investment</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Thailand</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Suksawat Terminal, Samut Prakan</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
+      <x:c r="J26" t="str">
+        <x:v>Binding agreement</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>River terminal; 48,000 sqm site; ~5,000 TEU static yard capacity; barge link to Laem Chabang</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>First operating foothold in Thailand and platform for Southeast Asia expansion</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>SRC_0380</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>Strategic equity investment</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>Equity investment</x:v>
+      </x:c>
+      <x:c r="P26" t="str">
+        <x:v>Southeast Asia</x:v>
+      </x:c>
+      <x:c r="Q26" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R26" t="str">
+        <x:v>Undisclosed</x:v>
+      </x:c>
+      <x:c r="S26" t="str">
+        <x:v>Announced / binding agreement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>INV026</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Q1 2026 organic capital expenditure</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Global / UAE</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Group portfolio</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>2026-03-31</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>1350000000</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I27"/>
+      <x:c r="J27" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>Quarterly organic CapEx; majority to Maritime &amp; Shipping and infrastructure</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>Infrastructure-led expansion programme</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>SRC_0383</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>Infrastructure programme</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="Q27" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R27" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S27" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>INV027</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Q2 2026 organic capital expenditure</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Global / UAE</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Group portfolio</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>1450000000</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I28"/>
+      <x:c r="J28" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>Quarterly organic CapEx excluding additional GFS stake acquisition</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>Infrastructure-led expansion programme</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>SRC_0384</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>Infrastructure programme</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P28" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="Q28" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R28" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S28" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>INV028</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Additional 30% stake in GFS</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>United Arab Emirates / Global</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Gulf Feeder Shipping</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>2026-06-23</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>1100000000</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>AED</x:v>
+      </x:c>
+      <x:c r="I29"/>
+      <x:c r="J29" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>Additional 30% stake acquisition</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Deepens control of feeder-shipping platform</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>SRC_0384</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>Acquisition / M&amp;A</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="P29" t="str">
+        <x:v>Middle East / Global</x:v>
+      </x:c>
+      <x:c r="Q29" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R29" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S29" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>INV029</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Caucedo Free Trade Zone logistics expansion</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Dominican Republic</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>DP World Free Trade Zone, Caucedo</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>2026-05-26</x:v>
+      </x:c>
+      <x:c r="G30" t="n">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>Committed</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>Additional warehousing and logistics infrastructure; adds to prior US$760m commitment</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>Americas manufacturing and logistics hub expansion</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>SRC_0386</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>Logistics infrastructure</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P30" t="str">
+        <x:v>Latin America / Caribbean</x:v>
+      </x:c>
+      <x:c r="Q30" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R30" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S30" t="str">
+        <x:v>Committed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>INV030</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Southampton quay crane programme</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>DP World Southampton</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>2026-06-19</x:v>
+      </x:c>
+      <x:c r="G31" t="n">
+        <x:v>60000000</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="I31"/>
+      <x:c r="J31" t="str">
+        <x:v>Actual / delivery</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>Four new quay cranes across 2026</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>Capacity and productivity upgrade at major UK gateway</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>SRC_0387</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>Terminal equipment</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q31" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R31" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S31" t="str">
+        <x:v>Actual / ongoing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>INV031</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Antwerp temperature-controlled logistics hub</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Belgium</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Port of Antwerp</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+      <x:c r="G32" t="n">
+        <x:v>48000000</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>EUR</x:v>
+      </x:c>
+      <x:c r="I32"/>
+      <x:c r="J32" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Initial €48m phase; long-term investment approximately €100m</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Cold-chain expansion adjacent to Antwerp Gateway</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>SRC_0388</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>Logistics infrastructure</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="Q32" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R32" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S32" t="str">
+        <x:v>Committed / development</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>INV032</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Fraser Surrey rail yard expansion</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>Fraser Surrey Terminal</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>2026-05-14</x:v>
+      </x:c>
+      <x:c r="G33" t="n">
+        <x:v>13300000</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>CAD</x:v>
+      </x:c>
+      <x:c r="I33"/>
+      <x:c r="J33" t="str">
+        <x:v>Construction</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>Rail track expansion from ~7.2km to ~13km usable track</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>Improves Canadian agri-export and intermodal resilience</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>SRC_0389</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>Rail / terminal infrastructure</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>CAPEX</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="Q33" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="R33" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="S33" t="str">
+        <x:v>Actual / construction</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/07_corporate_markets.xlsx
+++ b/data/07_corporate_markets.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R5f11c20cd5704429"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R666d4c9ca4be4793"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R7c80b1df88964ab8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R04003efea8b249e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="Recab40bcd4e140dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R0f625c6f2b594df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R5fc42d8174c848ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R6f1b016039bb4103"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="Rdc79be1b3a9941a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R2d70105ec5764489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R56a0871951b440ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="R58a4aa8a65514e48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R1a9b50915dd3448f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R06caf217de2141cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R5b0e70abadd54107"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R91a2c66f92154cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R70bcea4a9b364626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="Rfa1d853bae9743aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R4e831eeff77b41c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R7ed9d63ed6434fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R3e26c299c9e64abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R5caaab2fc04543ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R7befb39aff2f4299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R066905654bde4053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R6489f83ef95b415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R691e0d8085bd4033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="Rc0583f4bd5b24d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="Rba380cd030884f6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R5e5447da27934623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="Rfdc253fc0c954248"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -760,41 +760,6 @@
         <x:v>Includes official 2024 monthly share-price table</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Annual report / results</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>2026-03-12</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>DP World FY2025 results and annual report</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>https://www.dpworld.com/en/investors/annual-report-2025</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>Available</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>Record 2025 financials and capital expenditure</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -943,770 +908,6 @@
         <x:v>Canonical MBS company ID to align if already present</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>FIN134_001</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>COMP_HUNTER_GROUP</x:v>
-      </x:c>
-      <x:c r="C5" t="str"/>
-      <x:c r="D5" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>Disputed charter-rate receivable</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>55000000</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>Tanker chartering</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>Claimed underpayment; amount increased by about USD 12m from the prior month. Counterparty identity not confirmed in the current article; court case pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>FIN_ADP_2025_REV</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>RPT_001</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>Revenue</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>20770000000</x:v>
-      </x:c>
-      <x:c r="G6" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H6" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I6" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>FIN_ADP_2025_EBITDA</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>RPT_001</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>EBITDA</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>5110000000</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>FIN_ADP_2025_NP</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>RPT_001</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>Net profit</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>2070000000</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H8" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I8" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
-        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
-      </x:c>
-      <x:c r="K8" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>FIN_ADP_2025_CFO</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>RPT_001</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>Operating cash flow</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>5050000000</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I9" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/02/12/ad-ports-group-reports-record-2025-revenue</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>FIN_ADP_2025_CAPEX</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>RPT_001</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>Organic CAPEX</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>5500000000</x:v>
-      </x:c>
-      <x:c r="G10" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H10" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I10" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/02/12/ad-ports-group-reports-record-2025-revenue</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>FIN_ADP_2025_ASSETS</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>RPT_001</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>Total assets</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>69420000000</x:v>
-      </x:c>
-      <x:c r="G11" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>https://www.adportsgroup.com/en/investors/annual-report</x:v>
-      </x:c>
-      <x:c r="K11" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>FIN_ADP_Q2_26_REV</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>Revenue</x:v>
-      </x:c>
-      <x:c r="F12" t="n">
-        <x:v>7080000000</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>Q2 2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>FIN_ADP_Q2_26_EBITDA</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>EBITDA</x:v>
-      </x:c>
-      <x:c r="F13" t="n">
-        <x:v>1740000000</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>Q2 2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>FIN_ADP_Q2_26_NP</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>Net profit</x:v>
-      </x:c>
-      <x:c r="F14" t="n">
-        <x:v>836000000</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>Q2 2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>FIN_ADP_Q2_26_CFO</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>Operating cash flow</x:v>
-      </x:c>
-      <x:c r="F15" t="n">
-        <x:v>2140000000</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I15" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J15" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K15" t="str">
-        <x:v>Q2 2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>FIN_ADP_Q2_26_CAPEX</x:v>
-      </x:c>
-      <x:c r="B16" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
-        <x:v>Organic CAPEX</x:v>
-      </x:c>
-      <x:c r="F16" t="n">
-        <x:v>1450000000</x:v>
-      </x:c>
-      <x:c r="G16" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H16" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I16" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J16" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K16" t="str">
-        <x:v>Q2 2026; excludes GFS stake purchase</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>FIN_ADP_Q2_26_NETDEBT</x:v>
-      </x:c>
-      <x:c r="B17" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
-        <x:v>Net debt</x:v>
-      </x:c>
-      <x:c r="F17" t="n">
-        <x:v>22730000000</x:v>
-      </x:c>
-      <x:c r="G17" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I17" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J17" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K17" t="str">
-        <x:v>Q2 2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
-        <x:v>FIN_ADP_Q2_26_LEV</x:v>
-      </x:c>
-      <x:c r="B18" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
-        <x:v>Net debt / EBITDA</x:v>
-      </x:c>
-      <x:c r="F18" t="n">
-        <x:v>3.7</x:v>
-      </x:c>
-      <x:c r="G18" t="str">
-        <x:v>multiple</x:v>
-      </x:c>
-      <x:c r="H18"/>
-      <x:c r="I18" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J18" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K18" t="str">
-        <x:v>Q2 2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>FIN_ADP_Q2_26_FCFF</x:v>
-      </x:c>
-      <x:c r="B19" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>RPT_002</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>Free cash flow to firm</x:v>
-      </x:c>
-      <x:c r="F19" t="n">
-        <x:v>-1030000000</x:v>
-      </x:c>
-      <x:c r="G19" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H19" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I19" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J19" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/08/14/ad-ports-group-reports-q2-2026-net-profit-of-aed-836-million-demonstrating-strong-performance</x:v>
-      </x:c>
-      <x:c r="K19" t="str">
-        <x:v>Includes AED1.1bn GFS stake acquisition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
-        <x:v>FIN_DPW_2025_REV</x:v>
-      </x:c>
-      <x:c r="B20" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>Revenue</x:v>
-      </x:c>
-      <x:c r="F20" t="n">
-        <x:v>24400000000</x:v>
-      </x:c>
-      <x:c r="G20" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I20" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J20" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>FIN_DPW_2025_EBITDA</x:v>
-      </x:c>
-      <x:c r="B21" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>Adjusted EBITDA</x:v>
-      </x:c>
-      <x:c r="F21" t="n">
-        <x:v>6400000000</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I21" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J21" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K21" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>FIN_DPW_2025_PROFIT</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>Profit for the year</x:v>
-      </x:c>
-      <x:c r="F22" t="n">
-        <x:v>1960000000</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K22" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>FIN_DPW_2025_CFO</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
-        <x:v>Operating cash flow</x:v>
-      </x:c>
-      <x:c r="F23" t="n">
-        <x:v>6300000000</x:v>
-      </x:c>
-      <x:c r="G23" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I23" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J23" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K23" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>FIN_DPW_2025_CAPEX</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E24" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="F24" t="n">
-        <x:v>3100000000</x:v>
-      </x:c>
-      <x:c r="G24" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H24" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I24" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J24" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K24" t="str">
-        <x:v>FY2025 actual</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>FIN_DPW_2025_ROCE</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>Return on capital employed</x:v>
-      </x:c>
-      <x:c r="F25" t="n">
-        <x:v>9.9</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>percent</x:v>
-      </x:c>
-      <x:c r="H25"/>
-      <x:c r="I25" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J25" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K25" t="str">
-        <x:v>FY2025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>FIN_DPW_2026_CAPEX_BUDGET</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>RPT_006</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>2026-12-31</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>CAPEX budget</x:v>
-      </x:c>
-      <x:c r="F26" t="n">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>currency</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I26" t="str">
-        <x:v>Group</x:v>
-      </x:c>
-      <x:c r="J26" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="K26" t="str">
-        <x:v>Approximate 2026 budget; not actual spend</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1982,134 +1183,6 @@
       </x:c>
       <x:c r="J8" s="14" t="str">
         <x:v>Canadian Coast Guard Program Icebreakers</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>OPM_GULF_001</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>Khorfakkan future port capacity</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>TEU</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
-      <x:c r="I9" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>Long-term masterplan exceeds 10m TEU</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>OPM_GULF_002</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>Combined inland logistics capacity</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>2300000</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>TEU</x:v>
-      </x:c>
-      <x:c r="G10" t="str">
-        <x:v>Logistics / inland</x:v>
-      </x:c>
-      <x:c r="H10" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
-      <x:c r="I10" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>Al Dhaid and Sajaa combined</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>OPM_GULF_003</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>GT Lines fleet</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
-        <x:v>chartered vessels</x:v>
-      </x:c>
-      <x:c r="G11" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>Regional / Asia</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>Owned-vessel expansion underway</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>OPM_DPW_2025_TEU</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>2025-12-31</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>Gross container throughput</x:v>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>93400000</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>TEU</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>https://www.dpworld.com/en/news/releases/uae/dp-world-reports-record-244-bn-revenue-and-64bn-ebitda-for-2025</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>FY2025</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4801,24 +3874,6 @@
       <x:c r="M1" s="11" t="str">
         <x:v>Source ID</x:v>
       </x:c>
-      <x:c r="N1" t="str">
-        <x:v>Investment Class</x:v>
-      </x:c>
-      <x:c r="O1" t="str">
-        <x:v>Spend Type</x:v>
-      </x:c>
-      <x:c r="P1" t="str">
-        <x:v>Region</x:v>
-      </x:c>
-      <x:c r="Q1" t="str">
-        <x:v>Fiscal Year</x:v>
-      </x:c>
-      <x:c r="R1" t="str">
-        <x:v>Value Status</x:v>
-      </x:c>
-      <x:c r="S1" t="str">
-        <x:v>Investment Stage</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
@@ -4858,24 +3913,6 @@
       <x:c r="M2" s="14" t="str">
         <x:v>SRC_0031</x:v>
       </x:c>
-      <x:c r="N2" t="str">
-        <x:v>Infrastructure programme</x:v>
-      </x:c>
-      <x:c r="O2" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P2" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="Q2" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="R2" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S2" t="str">
-        <x:v>Actual / ongoing</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
@@ -4917,24 +3954,6 @@
       <x:c r="M3" s="14" t="str">
         <x:v>SRC_0004</x:v>
       </x:c>
-      <x:c r="N3" t="str">
-        <x:v>Terminal development</x:v>
-      </x:c>
-      <x:c r="O3" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P3" t="str">
-        <x:v>Middle East</x:v>
-      </x:c>
-      <x:c r="Q3" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R3" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S3" t="str">
-        <x:v>Committed / development</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
@@ -4976,24 +3995,6 @@
       <x:c r="M4" s="14" t="str">
         <x:v>SRC_0028</x:v>
       </x:c>
-      <x:c r="N4" t="str">
-        <x:v>Acquisition / M&amp;A</x:v>
-      </x:c>
-      <x:c r="O4" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P4" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="Q4" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R4" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S4" t="str">
-        <x:v>Pending / committed</x:v>
-      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -5035,24 +4036,6 @@
       <x:c r="M5" s="14" t="str">
         <x:v>SRC_0044</x:v>
       </x:c>
-      <x:c r="N5" t="str">
-        <x:v>Terminal expansion</x:v>
-      </x:c>
-      <x:c r="O5" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P5" t="str">
-        <x:v>Latin America</x:v>
-      </x:c>
-      <x:c r="Q5" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R5" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S5" t="str">
-        <x:v>Actual / commissioned</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
@@ -5094,24 +4077,6 @@
       <x:c r="M6" s="14" t="str">
         <x:v>SRC_0044</x:v>
       </x:c>
-      <x:c r="N6" t="str">
-        <x:v>Terminal expansion</x:v>
-      </x:c>
-      <x:c r="O6" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P6" t="str">
-        <x:v>Latin America</x:v>
-      </x:c>
-      <x:c r="Q6" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R6" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S6" t="str">
-        <x:v>Committed / construction</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
@@ -5151,24 +4116,6 @@
       <x:c r="M7" s="14" t="str">
         <x:v>SRC_0018</x:v>
       </x:c>
-      <x:c r="N7" t="str">
-        <x:v>Terminal development</x:v>
-      </x:c>
-      <x:c r="O7" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P7" t="str">
-        <x:v>Latin America</x:v>
-      </x:c>
-      <x:c r="Q7" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R7" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S7" t="str">
-        <x:v>Committed / development</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
@@ -5210,24 +4157,6 @@
       <x:c r="M8" s="14" t="str">
         <x:v>SRC_0034</x:v>
       </x:c>
-      <x:c r="N8" t="str">
-        <x:v>Infrastructure programme</x:v>
-      </x:c>
-      <x:c r="O8" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P8" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="Q8" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="R8" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S8" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -5267,24 +4196,6 @@
       <x:c r="M9" s="14" t="str">
         <x:v>SRC_0010</x:v>
       </x:c>
-      <x:c r="N9" t="str">
-        <x:v>Acquisition / M&amp;A</x:v>
-      </x:c>
-      <x:c r="O9" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P9" t="str">
-        <x:v>Latin America</x:v>
-      </x:c>
-      <x:c r="Q9" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R9" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S9" t="str">
-        <x:v>Announced / pending</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
@@ -5323,24 +4234,6 @@
       </x:c>
       <x:c r="M10" s="14" t="str">
         <x:v>SRC_0010</x:v>
-      </x:c>
-      <x:c r="N10" t="str">
-        <x:v>Port infrastructure</x:v>
-      </x:c>
-      <x:c r="O10" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P10" t="str">
-        <x:v>Middle East</x:v>
-      </x:c>
-      <x:c r="Q10" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R10" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S10" t="str">
-        <x:v>Committed</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5377,24 +4270,6 @@
       <x:c r="M11" s="14" t="str">
         <x:v>SRC_0041</x:v>
       </x:c>
-      <x:c r="N11" t="str">
-        <x:v>Logistics corridor development</x:v>
-      </x:c>
-      <x:c r="O11" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P11" t="str">
-        <x:v>Middle East</x:v>
-      </x:c>
-      <x:c r="Q11" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R11" t="str">
-        <x:v>Undisclosed</x:v>
-      </x:c>
-      <x:c r="S11" t="str">
-        <x:v>Committed / development</x:v>
-      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -5434,24 +4309,6 @@
       <x:c r="M12" s="14" t="str">
         <x:v>SRC_0007</x:v>
       </x:c>
-      <x:c r="N12" t="str">
-        <x:v>Port infrastructure</x:v>
-      </x:c>
-      <x:c r="O12" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P12" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q12" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R12" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S12" t="str">
-        <x:v>Actual / ongoing</x:v>
-      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
@@ -5491,24 +4348,6 @@
       <x:c r="M13" s="14" t="str">
         <x:v>SRC_0002</x:v>
       </x:c>
-      <x:c r="N13" t="str">
-        <x:v>Infrastructure programme</x:v>
-      </x:c>
-      <x:c r="O13" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P13" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q13" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="R13" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S13" t="str">
-        <x:v>Planned / multi-year</x:v>
-      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
@@ -5550,24 +4389,6 @@
       <x:c r="M14" s="14" t="str">
         <x:v>SRC_0256</x:v>
       </x:c>
-      <x:c r="N14" t="str">
-        <x:v>Strategic equity investment</x:v>
-      </x:c>
-      <x:c r="O14" t="str">
-        <x:v>Equity investment</x:v>
-      </x:c>
-      <x:c r="P14" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="Q14" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R14" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S14" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
@@ -5609,24 +4430,6 @@
       <x:c r="M15" s="14" t="str">
         <x:v>SRC_0255</x:v>
       </x:c>
-      <x:c r="N15" t="str">
-        <x:v>Asset disposal</x:v>
-      </x:c>
-      <x:c r="O15" t="str">
-        <x:v>Divestment</x:v>
-      </x:c>
-      <x:c r="P15" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q15" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="R15" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S15" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
@@ -5666,24 +4469,6 @@
       <x:c r="M16" s="14" t="str">
         <x:v>SRC_0263</x:v>
       </x:c>
-      <x:c r="N16" t="str">
-        <x:v>Logistics real estate</x:v>
-      </x:c>
-      <x:c r="O16" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P16" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q16" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R16" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S16" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
@@ -5725,24 +4510,6 @@
       <x:c r="M17" s="14" t="str">
         <x:v>SRC_0267</x:v>
       </x:c>
-      <x:c r="N17" t="str">
-        <x:v>Logistics real estate</x:v>
-      </x:c>
-      <x:c r="O17" t="str">
-        <x:v>Equity investment</x:v>
-      </x:c>
-      <x:c r="P17" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="Q17" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R17" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S17" t="str">
-        <x:v>Formed</x:v>
-      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
@@ -5782,24 +4549,6 @@
       <x:c r="M18" s="14" t="str">
         <x:v>SRC_0268</x:v>
       </x:c>
-      <x:c r="N18" t="str">
-        <x:v>Logistics real estate</x:v>
-      </x:c>
-      <x:c r="O18" t="str">
-        <x:v>Equity investment</x:v>
-      </x:c>
-      <x:c r="P18" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q18" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R18" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S18" t="str">
-        <x:v>Formed</x:v>
-      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
@@ -5840,24 +4589,6 @@
       </x:c>
       <x:c r="M19" s="14" t="str">
         <x:v>SRC_0258</x:v>
-      </x:c>
-      <x:c r="N19" t="str">
-        <x:v>Acquisition / M&amp;A</x:v>
-      </x:c>
-      <x:c r="O19" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P19" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="Q19" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="R19" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S19" t="str">
-        <x:v>Completed</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5894,24 +4625,6 @@
       <x:c r="M20" s="14" t="str">
         <x:v>SRC_0277</x:v>
       </x:c>
-      <x:c r="N20" t="str">
-        <x:v>Acquisition / M&amp;A</x:v>
-      </x:c>
-      <x:c r="O20" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P20" t="str">
-        <x:v>Central Asia / Caucasus</x:v>
-      </x:c>
-      <x:c r="Q20" t="n">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c r="R20" t="str">
-        <x:v>Undisclosed</x:v>
-      </x:c>
-      <x:c r="S20" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
@@ -5952,24 +4665,6 @@
       </x:c>
       <x:c r="M21" s="14" t="str">
         <x:v>SRC_0281</x:v>
-      </x:c>
-      <x:c r="N21" t="str">
-        <x:v>Economic zone development</x:v>
-      </x:c>
-      <x:c r="O21" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P21" t="str">
-        <x:v>Middle East / North Africa</x:v>
-      </x:c>
-      <x:c r="Q21" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="R21" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S21" t="str">
-        <x:v>Committed / development</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6006,24 +4701,6 @@
       <x:c r="M22" s="14" t="str">
         <x:v>SRC_0285</x:v>
       </x:c>
-      <x:c r="N22" t="str">
-        <x:v>Logistics real estate</x:v>
-      </x:c>
-      <x:c r="O22" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P22" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="Q22" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R22" t="str">
-        <x:v>Undisclosed</x:v>
-      </x:c>
-      <x:c r="S22" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
@@ -6063,24 +4740,6 @@
       <x:c r="M23" s="14" t="str">
         <x:v>SRC_0296</x:v>
       </x:c>
-      <x:c r="N23" t="str">
-        <x:v>Logistics hub development</x:v>
-      </x:c>
-      <x:c r="O23" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P23" t="str">
-        <x:v>Middle East</x:v>
-      </x:c>
-      <x:c r="Q23" t="n">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c r="R23" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S23" t="str">
-        <x:v>Committed / development</x:v>
-      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
@@ -6122,24 +4781,6 @@
       <x:c r="M24" s="14" t="str">
         <x:v>SRC_0300</x:v>
       </x:c>
-      <x:c r="N24" t="str">
-        <x:v>Air cargo infrastructure</x:v>
-      </x:c>
-      <x:c r="O24" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P24" t="str">
-        <x:v>South Asia</x:v>
-      </x:c>
-      <x:c r="Q24" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R24" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S24" t="str">
-        <x:v>Committed / development</x:v>
-      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
@@ -6180,478 +4821,6 @@
       </x:c>
       <x:c r="M25" s="14" t="str">
         <x:v>SRC_0306</x:v>
-      </x:c>
-      <x:c r="N25" t="str">
-        <x:v>Air cargo infrastructure</x:v>
-      </x:c>
-      <x:c r="O25" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P25" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="Q25" t="n">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c r="R25" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S25" t="str">
-        <x:v>Actual / operating</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>INV025</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>Suksawat Terminal strategic investment</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>Thailand</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>Suksawat Terminal, Samut Prakan</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-      <x:c r="I26"/>
-      <x:c r="J26" t="str">
-        <x:v>Binding agreement</x:v>
-      </x:c>
-      <x:c r="K26" t="str">
-        <x:v>River terminal; 48,000 sqm site; ~5,000 TEU static yard capacity; barge link to Laem Chabang</x:v>
-      </x:c>
-      <x:c r="L26" t="str">
-        <x:v>First operating foothold in Thailand and platform for Southeast Asia expansion</x:v>
-      </x:c>
-      <x:c r="M26" t="str">
-        <x:v>SRC_0380</x:v>
-      </x:c>
-      <x:c r="N26" t="str">
-        <x:v>Strategic equity investment</x:v>
-      </x:c>
-      <x:c r="O26" t="str">
-        <x:v>Equity investment</x:v>
-      </x:c>
-      <x:c r="P26" t="str">
-        <x:v>Southeast Asia</x:v>
-      </x:c>
-      <x:c r="Q26" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R26" t="str">
-        <x:v>Undisclosed</x:v>
-      </x:c>
-      <x:c r="S26" t="str">
-        <x:v>Announced / binding agreement</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>INV026</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>Q1 2026 organic capital expenditure</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>Global / UAE</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
-        <x:v>Group portfolio</x:v>
-      </x:c>
-      <x:c r="F27" t="str">
-        <x:v>2026-03-31</x:v>
-      </x:c>
-      <x:c r="G27" t="n">
-        <x:v>1350000000</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I27"/>
-      <x:c r="J27" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="K27" t="str">
-        <x:v>Quarterly organic CapEx; majority to Maritime &amp; Shipping and infrastructure</x:v>
-      </x:c>
-      <x:c r="L27" t="str">
-        <x:v>Infrastructure-led expansion programme</x:v>
-      </x:c>
-      <x:c r="M27" t="str">
-        <x:v>SRC_0383</x:v>
-      </x:c>
-      <x:c r="N27" t="str">
-        <x:v>Infrastructure programme</x:v>
-      </x:c>
-      <x:c r="O27" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P27" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="Q27" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R27" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S27" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
-        <x:v>INV027</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>Q2 2026 organic capital expenditure</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>Global / UAE</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
-        <x:v>Group portfolio</x:v>
-      </x:c>
-      <x:c r="F28" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="G28" t="n">
-        <x:v>1450000000</x:v>
-      </x:c>
-      <x:c r="H28" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I28"/>
-      <x:c r="J28" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="K28" t="str">
-        <x:v>Quarterly organic CapEx excluding additional GFS stake acquisition</x:v>
-      </x:c>
-      <x:c r="L28" t="str">
-        <x:v>Infrastructure-led expansion programme</x:v>
-      </x:c>
-      <x:c r="M28" t="str">
-        <x:v>SRC_0384</x:v>
-      </x:c>
-      <x:c r="N28" t="str">
-        <x:v>Infrastructure programme</x:v>
-      </x:c>
-      <x:c r="O28" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P28" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="Q28" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R28" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S28" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
-        <x:v>INV028</x:v>
-      </x:c>
-      <x:c r="B29" t="str">
-        <x:v>COMP_ADPORTS</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>Additional 30% stake in GFS</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>United Arab Emirates / Global</x:v>
-      </x:c>
-      <x:c r="E29" t="str">
-        <x:v>Gulf Feeder Shipping</x:v>
-      </x:c>
-      <x:c r="F29" t="str">
-        <x:v>2026-06-23</x:v>
-      </x:c>
-      <x:c r="G29" t="n">
-        <x:v>1100000000</x:v>
-      </x:c>
-      <x:c r="H29" t="str">
-        <x:v>AED</x:v>
-      </x:c>
-      <x:c r="I29"/>
-      <x:c r="J29" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
-      <x:c r="K29" t="str">
-        <x:v>Additional 30% stake acquisition</x:v>
-      </x:c>
-      <x:c r="L29" t="str">
-        <x:v>Deepens control of feeder-shipping platform</x:v>
-      </x:c>
-      <x:c r="M29" t="str">
-        <x:v>SRC_0384</x:v>
-      </x:c>
-      <x:c r="N29" t="str">
-        <x:v>Acquisition / M&amp;A</x:v>
-      </x:c>
-      <x:c r="O29" t="str">
-        <x:v>M&amp;A</x:v>
-      </x:c>
-      <x:c r="P29" t="str">
-        <x:v>Middle East / Global</x:v>
-      </x:c>
-      <x:c r="Q29" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R29" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S29" t="str">
-        <x:v>Completed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="str">
-        <x:v>INV029</x:v>
-      </x:c>
-      <x:c r="B30" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>Caucedo Free Trade Zone logistics expansion</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>Dominican Republic</x:v>
-      </x:c>
-      <x:c r="E30" t="str">
-        <x:v>DP World Free Trade Zone, Caucedo</x:v>
-      </x:c>
-      <x:c r="F30" t="str">
-        <x:v>2026-05-26</x:v>
-      </x:c>
-      <x:c r="G30" t="n">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="H30" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I30" t="n">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="J30" t="str">
-        <x:v>Committed</x:v>
-      </x:c>
-      <x:c r="K30" t="str">
-        <x:v>Additional warehousing and logistics infrastructure; adds to prior US$760m commitment</x:v>
-      </x:c>
-      <x:c r="L30" t="str">
-        <x:v>Americas manufacturing and logistics hub expansion</x:v>
-      </x:c>
-      <x:c r="M30" t="str">
-        <x:v>SRC_0386</x:v>
-      </x:c>
-      <x:c r="N30" t="str">
-        <x:v>Logistics infrastructure</x:v>
-      </x:c>
-      <x:c r="O30" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P30" t="str">
-        <x:v>Latin America / Caribbean</x:v>
-      </x:c>
-      <x:c r="Q30" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R30" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S30" t="str">
-        <x:v>Committed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str">
-        <x:v>INV030</x:v>
-      </x:c>
-      <x:c r="B31" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>Southampton quay crane programme</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>United Kingdom</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>DP World Southampton</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>2026-06-19</x:v>
-      </x:c>
-      <x:c r="G31" t="n">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="H31" t="str">
-        <x:v>GBP</x:v>
-      </x:c>
-      <x:c r="I31"/>
-      <x:c r="J31" t="str">
-        <x:v>Actual / delivery</x:v>
-      </x:c>
-      <x:c r="K31" t="str">
-        <x:v>Four new quay cranes across 2026</x:v>
-      </x:c>
-      <x:c r="L31" t="str">
-        <x:v>Capacity and productivity upgrade at major UK gateway</x:v>
-      </x:c>
-      <x:c r="M31" t="str">
-        <x:v>SRC_0387</x:v>
-      </x:c>
-      <x:c r="N31" t="str">
-        <x:v>Terminal equipment</x:v>
-      </x:c>
-      <x:c r="O31" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P31" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q31" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R31" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S31" t="str">
-        <x:v>Actual / ongoing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
-        <x:v>INV031</x:v>
-      </x:c>
-      <x:c r="B32" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>Antwerp temperature-controlled logistics hub</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>Belgium</x:v>
-      </x:c>
-      <x:c r="E32" t="str">
-        <x:v>Port of Antwerp</x:v>
-      </x:c>
-      <x:c r="F32" t="str">
-        <x:v>2026-08-05</x:v>
-      </x:c>
-      <x:c r="G32" t="n">
-        <x:v>48000000</x:v>
-      </x:c>
-      <x:c r="H32" t="str">
-        <x:v>EUR</x:v>
-      </x:c>
-      <x:c r="I32"/>
-      <x:c r="J32" t="str">
-        <x:v>Development</x:v>
-      </x:c>
-      <x:c r="K32" t="str">
-        <x:v>Initial €48m phase; long-term investment approximately €100m</x:v>
-      </x:c>
-      <x:c r="L32" t="str">
-        <x:v>Cold-chain expansion adjacent to Antwerp Gateway</x:v>
-      </x:c>
-      <x:c r="M32" t="str">
-        <x:v>SRC_0388</x:v>
-      </x:c>
-      <x:c r="N32" t="str">
-        <x:v>Logistics infrastructure</x:v>
-      </x:c>
-      <x:c r="O32" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P32" t="str">
-        <x:v>Europe</x:v>
-      </x:c>
-      <x:c r="Q32" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R32" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S32" t="str">
-        <x:v>Committed / development</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="str">
-        <x:v>INV032</x:v>
-      </x:c>
-      <x:c r="B33" t="str">
-        <x:v>COMP_DPW</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>Fraser Surrey rail yard expansion</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
-        <x:v>Fraser Surrey Terminal</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
-        <x:v>2026-05-14</x:v>
-      </x:c>
-      <x:c r="G33" t="n">
-        <x:v>13300000</x:v>
-      </x:c>
-      <x:c r="H33" t="str">
-        <x:v>CAD</x:v>
-      </x:c>
-      <x:c r="I33"/>
-      <x:c r="J33" t="str">
-        <x:v>Construction</x:v>
-      </x:c>
-      <x:c r="K33" t="str">
-        <x:v>Rail track expansion from ~7.2km to ~13km usable track</x:v>
-      </x:c>
-      <x:c r="L33" t="str">
-        <x:v>Improves Canadian agri-export and intermodal resilience</x:v>
-      </x:c>
-      <x:c r="M33" t="str">
-        <x:v>SRC_0389</x:v>
-      </x:c>
-      <x:c r="N33" t="str">
-        <x:v>Rail / terminal infrastructure</x:v>
-      </x:c>
-      <x:c r="O33" t="str">
-        <x:v>CAPEX</x:v>
-      </x:c>
-      <x:c r="P33" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="Q33" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="R33" t="str">
-        <x:v>Reported</x:v>
-      </x:c>
-      <x:c r="S33" t="str">
-        <x:v>Actual / construction</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/07_corporate_markets.xlsx
+++ b/data/07_corporate_markets.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R91a2c66f92154cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R70bcea4a9b364626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="Rfa1d853bae9743aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R4e831eeff77b41c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="R7ed9d63ed6434fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="R3e26c299c9e64abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="R5caaab2fc04543ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R7befb39aff2f4299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R066905654bde4053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R6489f83ef95b415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R691e0d8085bd4033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="Rc0583f4bd5b24d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="Rba380cd030884f6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="R5e5447da27934623"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="Rfdc253fc0c954248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rfd85f6d815e44b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="Rcfbe051c886e416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R781b6cfafb1d4b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R1e3dd757cdf0404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="Rde34df206d2843e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="Ref1758ecf63c44aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="Rf7290c75f63c4eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R9c088616ca414649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R998e91cb645e40cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R4bbd1cc399324493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="Rd6345e23c1034f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="R80f8785453134122"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R130dc873422d40c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="Rea4830b2c21e4cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R143ef6e74d69439a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2961,6 +2961,98 @@
         <x:v>2026-09-09</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>INVESTOR_BF_001</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>COMP_ATCO</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>ATCO Ltd.</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Listed diversified infrastructure investor / operator</x:v>
+      </x:c>
+      <x:c r="E31"/>
+      <x:c r="F31" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Transportation; energy; infrastructure; real estate; services</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>40% interest in Neltume Ports</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>ATCO Land &amp; Development</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>Neltume / port exposure through equity investment</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>ATCO reports 40% interest in Neltume Ports</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>Canonical</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>SRC_BF_ATCO_NELTUME</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>INVESTOR_BF_002</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Neltume Ports</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Strategic port operator / infrastructure developer</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Ultramar / ATCO</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Chile</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Port development; terminals; operations; stevedoring</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Montecon / Uruguay; 17 port facilities in portfolio</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>Port-linked logistics exposure</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>Montevideo and South American port network</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Proposed US$900m MCT greenfield terminal in Montevideo</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Canonical</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>SRC_BF_NELTUME_SPLASH</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3810,6 +3902,246 @@
         <x:v>Qube delisted 17 Aug 2026</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>HOLD_BF_001</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>COMP_ATCO</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>ATCO Ltd.</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Neltume Ports</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Port operator / infrastructure platform</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>South America</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>Equity / non-controlled interest</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>No / strategic minority</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>2018-09-01</x:v>
+      </x:c>
+      <x:c r="L19"/>
+      <x:c r="M19" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>SRC_BF_ATCO_NELTUME</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>https://www.atco.com/en-ca/businesses/investments/neltume-ports.html</x:v>
+      </x:c>
+      <x:c r="P19" t="str">
+        <x:v>ATCO acquired 40% in 2018.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>HOLD_BF_002</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>COMP_MARSA_MAROC</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Marsa Maroc</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>West Med Container Terminal</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Container terminal SPV</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Morocco</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>50% + 1 share</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>Equity</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>Shared / majority by one share</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>2026-01-21</x:v>
+      </x:c>
+      <x:c r="L20"/>
+      <x:c r="M20" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>SRC_BF_NADOR_MARSA26</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>https://www.marsamaroc.co.ma/sites/default/files/2026-01/CP%20%20WEST%20MED%20CONTAINER%20TERMINAL%20UK.pdf</x:v>
+      </x:c>
+      <x:c r="P20" t="str">
+        <x:v>WMCT concessionaire of Nador East terminal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>HOLD_BF_003</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>COMP_TIL</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Terminal Investment Limited</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>West Med Container Terminal</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Container terminal SPV</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Morocco</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>50% - 1 share</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Equity</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>Shared</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>2026-01-21</x:v>
+      </x:c>
+      <x:c r="L21"/>
+      <x:c r="M21" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>SRC_BF_NADOR_MARSA26</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>https://www.marsamaroc.co.ma/sites/default/files/2026-01/CP%20%20WEST%20MED%20CONTAINER%20TERMINAL%20UK.pdf</x:v>
+      </x:c>
+      <x:c r="P21" t="str">
+        <x:v>TIL entry completed after approvals.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>HOLD_BF_004</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>COMP_KATOEN_NATIE</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Katoen Natie</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Terminal Cuenca del Plata</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Container terminal operator</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Equity / majority interest</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>Yes / majority</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>2021-02-01</x:v>
+      </x:c>
+      <x:c r="L22"/>
+      <x:c r="M22" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>https://www.anp.com.uy/en/node/1154</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>ANP cites 80% private majority and 20% ANP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>HOLD_BF_005</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>COMP_ANP_URUGUAY</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Administración Nacional de Puertos</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Terminal Cuenca del Plata</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Container terminal operator</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Equity / public minority</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>2021-02-01</x:v>
+      </x:c>
+      <x:c r="L23"/>
+      <x:c r="M23" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>https://www.anp.com.uy/en/node/1154</x:v>
+      </x:c>
+      <x:c r="P23" t="str">
+        <x:v>Public minority stake.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4821,6 +5153,170 @@
       </x:c>
       <x:c r="M25" s="14" t="str">
         <x:v>SRC_0306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>INV025</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>COMP_CMA_TERMINALS</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Beirut Container Terminal modernization plan</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>Lebanon</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>2022-02-17</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>Operating / implemented</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>10-year concession; infrastructure, equipment, digital and environmental upgrades</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>Reconstruction and operational control of Lebanon's main container gateway</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>SRC_BF_BEIRUT_CMA22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>INV026</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>COMP_CMA_TERMINALS</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Beirut Container Terminal expansion</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Lebanon</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Launched</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>Capacity from ~1.3m to 3.0m TEU by 2028</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>Eastern Mediterranean and Levant hub expansion</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>SRC_BF_BEIRUT_SPLASH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>INV027</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Montevideo Container Terminal (MCT) proposal</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Port of Montevideo</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>900000000</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>900000000</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>Proposed / government evaluation</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>1.15m TEU; 940m quay; ~38ha; independent access; ~1,800 construction jobs</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>Potential largest private port investment proposal in Uruguay; changes competitive structure</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>SRC_BF_NELTUME_SPLASH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>INV028</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Terminal Cuenca del Plata expansion programme</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Port of Montevideo</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>2023-07-24</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>Authorized / development</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>&gt;US$600m; 22ha yard + 700m quay</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Long-term Montevideo container capacity expansion and competitive benchmark</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5849,24 +6345,26 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>LIST_004</x:v>
+        <x:v>LIST_005</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>COMP_TFI_INTL</x:v>
+        <x:v>COMP_MARSA_MAROC</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>TFI International</x:v>
+        <x:v>Marsa Maroc (SODEP)</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>TSX / NYSE</x:v>
+        <x:v>Casablanca Stock Exchange</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>TFII</x:v>
-      </x:c>
-      <x:c r="F5" s="14"/>
+        <x:v>MSA</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>2016-07-19</x:v>
+      </x:c>
       <x:c r="G5" s="14"/>
       <x:c r="H5" s="14" t="str">
-        <x:v>CAD / USD</x:v>
+        <x:v>MAD</x:v>
       </x:c>
       <x:c r="I5" s="14"/>
       <x:c r="J5" s="14" t="str">
@@ -5874,13 +6372,85 @@
       </x:c>
       <x:c r="K5" s="14"/>
       <x:c r="L5" s="14" t="str">
-        <x:v>SRC_V125_008</x:v>
+        <x:v>SRC_BF_MARSA_LIST</x:v>
       </x:c>
       <x:c r="M5" s="14" t="str">
-        <x:v>https://tfiintl.com/</x:v>
+        <x:v>https://www.casablanca-bourse.com/live-market/instruments/MSA</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>Public parent of Canpar</x:v>
+        <x:v>ISIN MA0000012312</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>LIST_006</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>COMP_ATCO</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>ATCO Ltd. Class I</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Toronto Stock Exchange</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>ACO.X</x:v>
+      </x:c>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6" t="str">
+        <x:v>CAD</x:v>
+      </x:c>
+      <x:c r="I6"/>
+      <x:c r="J6" t="str">
+        <x:v>Listed</x:v>
+      </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6" t="str">
+        <x:v>SRC_BF_ATCO_LIST</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>https://www.atco.com/content/dam/atco-website/en-ca/web/assets/investors/atco-2025-special-meeting-circular.pdf</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>Class I non-voting shares</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>LIST_007</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>COMP_ATCO</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>ATCO Ltd. Class II</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Toronto Stock Exchange</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>ACO.Y</x:v>
+      </x:c>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7" t="str">
+        <x:v>CAD</x:v>
+      </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7" t="str">
+        <x:v>Listed</x:v>
+      </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
+        <x:v>SRC_BF_ATCO_LIST</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>https://www.atco.com/content/dam/atco-website/en-ca/web/assets/investors/atco-2025-special-meeting-circular.pdf</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>Class II voting shares</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7240,6 +7810,184 @@
       </x:c>
       <x:c r="L6" s="14"/>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>OWNH_BF_001</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>COMP_ATCO</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Equity investor</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>2018-09-01</x:v>
+      </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7" t="str">
+        <x:v>SRC_BF_ATCO_NELTUME</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>https://www.atco.com/en-ca/businesses/investments/neltume-ports.html</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>40% interest acquired in 2018.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>OWNH_BF_002</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>COMP_MARSA_MAROC</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Equity owner</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>50% + 1 share</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>2026-01-21</x:v>
+      </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>IDEAL_BF_001</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>SRC_BF_NADOR_MARSA26</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>https://www.marsamaroc.co.ma/sites/default/files/2026-01/CP%20%20WEST%20MED%20CONTAINER%20TERMINAL%20UK.pdf</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>Post-closing ownership.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>OWNH_BF_003</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>COMP_TIL</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Equity owner</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>50% - 1 share</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>2026-01-21</x:v>
+      </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>IDEAL_BF_001</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>SRC_BF_NADOR_MARSA26</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>https://www.marsamaroc.co.ma/sites/default/files/2026-01/CP%20%20WEST%20MED%20CONTAINER%20TERMINAL%20UK.pdf</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>Post-closing ownership.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>OWNH_BF_004</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>COMP_KATOEN_NATIE</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Majority owner</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>2021-02-01</x:v>
+      </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>IDEAL_BF_005</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>https://www.anp.com.uy/en/node/1154</x:v>
+      </x:c>
+      <x:c r="L10" t="str">
+        <x:v>Long-term TCP structure; concession extended in 2021 context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>OWNH_BF_005</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>COMP_ANP_URUGUAY</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Minority owner</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>2021-02-01</x:v>
+      </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>IDEAL_BF_005</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>https://www.anp.com.uy/en/node/1154</x:v>
+      </x:c>
+      <x:c r="L11" t="str">
+        <x:v>Public minority ownership.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/07_corporate_markets.xlsx
+++ b/data/07_corporate_markets.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rfd85f6d815e44b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="Rcfbe051c886e416d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R781b6cfafb1d4b14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R1e3dd757cdf0404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="Rde34df206d2843e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="Ref1758ecf63c44aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="Rf7290c75f63c4eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R9c088616ca414649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R998e91cb645e40cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="R4bbd1cc399324493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="Rd6345e23c1034f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="R80f8785453134122"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R130dc873422d40c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="Rea4830b2c21e4cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R143ef6e74d69439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R160e7d269c9b498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Investors" sheetId="2" r:id="R8094aef8fb484a96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Holdings" sheetId="3" r:id="R8db176d7461c4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investments" sheetId="4" r:id="R3c85996b26634406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistics Real Estate" sheetId="5" r:id="Rd03e93f7598d43f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Listings" sheetId="6" r:id="Ra7626e44ced74cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Market Prices" sheetId="7" r:id="Rf4563ea3b0e2499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Actions" sheetId="8" r:id="R0e3cb64daf7f4209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ownership History" sheetId="9" r:id="R5bebe1b8da2a4c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Reports" sheetId="10" r:id="Rd6f46c2bfc454118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Financial Metrics" sheetId="11" r:id="R3c3a2ae7b93c4b51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Operating Metrics" sheetId="12" r:id="Rd0b8c4fb61c44f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Funds" sheetId="13" r:id="R4fa9e55f4acf493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Holdings V125" sheetId="14" r:id="Rafd8e2b79263458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Aliases" sheetId="15" r:id="R897316da64f74b1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6453,6 +6453,78 @@
         <x:v>Class II voting shares</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>LIST_008</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd.</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>National Stock Exchange of India</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8" t="str">
+        <x:v>INR</x:v>
+      </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8" t="str">
+        <x:v>Listed</x:v>
+      </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8" t="str">
+        <x:v>SRC_SAGAR_GRSE_CONTRACT</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+      <x:c r="N8" t="str">
+        <x:v>Official GRSE exchange filing identifies NSE symbol GRSE.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>LIST_009</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Garden Reach Shipbuilders &amp; Engineers Ltd.</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>BSE Limited</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>542011</x:v>
+      </x:c>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9" t="str">
+        <x:v>INR</x:v>
+      </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9" t="str">
+        <x:v>Listed</x:v>
+      </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>Official GRSE exchange filing identifies BSE scrip code 542011.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
